--- a/허브누리_레시피_목록_상세_p4of6_썸네일.xlsx
+++ b/허브누리_레시피_목록_상세_p4of6_썸네일.xlsx
@@ -21787,7 +21787,7 @@
       <c r="I132" s="8" t="n"/>
       <c r="J132" s="8" t="n"/>
     </row>
-    <row r="133" ht="16" customHeight="1">
+    <row r="133" ht="16.15384615384615" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
           <t>아데노신BB크림</t>
@@ -21826,7 +21826,19 @@
 주사기를 이용하시면 좋습니다.</t>
         </is>
       </c>
-      <c r="H133" s="4" t="n"/>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>만들기 방법
+1~2. 오일/유화제를 용기 하나에 계량하고 다른 용기에 라벤더워터를 계량하세요
+3. 70도가 될때까지 물을 동시에 데워주세요. 골고루 저어주세요
+4. 온도가 맞으면 워터를 오일/왁스에 넣어주세요
+5. 핸드블랜더 하시구요
+6~8. 온도가 내려가면 첨가물을 한꺼번에 다 넣어주세요. 아데노신, 페이스파우더21호, 티타늄디옥사이드 등등....
+9. 스푼으로 골고루 저어주시구요.
+10. 다시 핸드블랜더 해주세요
+11. 마지막으로 알뜰주걱으로 마무리~!</t>
+        </is>
+      </c>
       <c r="I133" s="4" t="n"/>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -21834,7 +21846,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="16" customHeight="1">
+    <row r="134" ht="16.15384615384615" customHeight="1">
       <c r="C134" t="inlineStr">
         <is>
           <t>로즈힙오일</t>
@@ -21856,7 +21868,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="16" customHeight="1">
+    <row r="135" ht="16.15384615384615" customHeight="1">
       <c r="C135" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
@@ -21878,7 +21890,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="16" customHeight="1">
+    <row r="136" ht="16.15384615384615" customHeight="1">
       <c r="C136" t="inlineStr">
         <is>
           <t>로즈워터</t>
@@ -21900,7 +21912,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="16" customHeight="1">
+    <row r="137" ht="16.15384615384615" customHeight="1">
       <c r="C137" t="inlineStr">
         <is>
           <t>한방보존제</t>
@@ -21922,7 +21934,7 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="16" customHeight="1">
+    <row r="138" ht="16.15384615384615" customHeight="1">
       <c r="C138" t="inlineStr">
         <is>
           <t>식물성플라센타</t>
@@ -21944,7 +21956,7 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="16" customHeight="1">
+    <row r="139" ht="16.15384615384615" customHeight="1">
       <c r="C139" t="inlineStr">
         <is>
           <t>아데노신</t>
@@ -21966,7 +21978,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="16" customHeight="1">
+    <row r="140" ht="16.15384615384615" customHeight="1">
       <c r="C140" t="inlineStr">
         <is>
           <t>히아루론산</t>
@@ -21988,7 +22000,7 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="16" customHeight="1">
+    <row r="141" ht="16.15384615384615" customHeight="1">
       <c r="C141" t="inlineStr">
         <is>
           <t>화이텐스</t>
@@ -22010,7 +22022,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="16" customHeight="1">
+    <row r="142" ht="16.15384615384615" customHeight="1">
       <c r="C142" t="inlineStr">
         <is>
           <t>시너메이트</t>
@@ -22032,7 +22044,7 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="16" customHeight="1">
+    <row r="143" ht="16.15384615384615" customHeight="1">
       <c r="C143" t="inlineStr">
         <is>
           <t>컬러믹스파운데이션</t>
@@ -22049,7 +22061,7 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="16" customHeight="1">
+    <row r="144" ht="16.15384615384615" customHeight="1">
       <c r="C144" t="inlineStr">
         <is>
           <t>티타늄디옥사이드</t>
@@ -22066,7 +22078,7 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="16" customHeight="1">
+    <row r="145" ht="16.15384615384615" customHeight="1">
       <c r="C145" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
@@ -22127,7 +22139,15 @@
 칸데릴라왁스 사용시 밀랍 사용시</t>
         </is>
       </c>
-      <c r="H146" s="7" t="n"/>
+      <c r="H146" s="7" t="inlineStr">
+        <is>
+          <t>만들기 방법
+1~4. 카렌듈라인퓨즈오일, 캐모마일인퓨즈오일, 비정제밀랍을 계량하고 잘 섞이도록 저으면서 녹입니다.
+5~6. 다 녹으면 50도 정도로 식혀서 에센셜오일을 넣고
+7~8. 골고루 섞은 후 용기에 부어주세요.
+9. 완성~!</t>
+        </is>
+      </c>
       <c r="I146" s="7" t="n"/>
       <c r="J146" s="6" t="inlineStr">
         <is>
@@ -24224,7 +24244,14 @@
 워셔블타입 티트리클렌징오일은 피지성분과 비슷한 호호바오일이 들어있어 끈적임이 없고 오일이기 때문에 피부의 피지, 노폐물등을 잘 분리할 수 있습니다. 또 물에 씻기는 타입이라 오일 잔존감이 없이 산뜻합니다. 티트리, 레몬에센셜오일은 상큼한 향기와 항균효과를 줍니다.</t>
         </is>
       </c>
-      <c r="H209" s="4" t="n"/>
+      <c r="H209" s="4" t="inlineStr">
+        <is>
+          <t>만들기 방법
+1~5. 호호바오일, 녹차씨오일, 올리브리퀴드, 티트리에센셜오일 등을 계량하기
+6. 골고루 섞어주기
+7. 용기에 넣기</t>
+        </is>
+      </c>
       <c r="I209" s="4" t="n"/>
       <c r="J209" s="3" t="inlineStr">
         <is>
@@ -24354,7 +24381,15 @@
 오스트레일리아 원주민들은 이미 오래전부터 티트리 나무의 잎으로 베인 상처에 생긴 감염증을 치료해왔답니다. 제2차 세계대전중에는 피부창상의 치료제로서 열대지방의 군인에게 지급키도하고 외과와 치과에서 사용되며 살균소독제, 탈취제, 비누,공기정화제에도 넣고 있습니다. 이밖에도 각종 감염증, 여드름, 벌레물린 곳, 감기, 입냄새, 무좀, 비듬 등에도 효과가 있습니다. 부분적으로 사용할 때 원액을 사용하지만 고농축이라 희석해서 사용하셔야 합니다. 티트리워터는 티트리를 이용 수증기증류법으로 얻을 수 있는데 티트리의 수용성성분이 다량 녹아있어 효능은 티트리에센셜오일과 비슷하면서 피부에 직접 사용할 수 있습니다.</t>
         </is>
       </c>
-      <c r="H214" s="7" t="n"/>
+      <c r="H214" s="7" t="inlineStr">
+        <is>
+          <t>만들기 방법
+1. 티트리워터, 편백워터를 계량합니다.
+2. 식물성글리세린을 기호에 맞게 조절하세요
+3. 천연한방보존제를 계량
+4. 골고루 섞어주시면 되요. 완성~!</t>
+        </is>
+      </c>
       <c r="I214" s="7" t="n"/>
       <c r="J214" s="6" t="inlineStr">
         <is>
@@ -25279,7 +25314,15 @@
 베이스오일에 원하는 에센셜오일을 떨어뜨려 흔들어 골고루 섞이기만 하면 된답니다.</t>
         </is>
       </c>
-      <c r="H243" s="4" t="n"/>
+      <c r="H243" s="4" t="inlineStr">
+        <is>
+          <t>만들기 방법
+1. 오일을 계량하고
+2. 에센셜오일을 떨어뜨린다
+3. 섞어주기
+4. 용기에 붓기</t>
+        </is>
+      </c>
       <c r="I243" s="4" t="n"/>
       <c r="J243" s="3" t="inlineStr">
         <is>
@@ -25384,7 +25427,18 @@
 라벤더EO 8방울</t>
         </is>
       </c>
-      <c r="H245" s="7" t="n"/>
+      <c r="H245" s="7" t="inlineStr">
+        <is>
+          <t>만들기 방법
+1. 오일/유화제를 용기에 계량하기
+2. 워터류를 다른 용기에 계량하기
+3. 70도로 저으면서 데우기
+4. 온도가 맞으면 워터를 오일에 섞기
+5. 핸드블랜더로 섞기
+6~7. 온도가 50도 이하로 떨어지면 에센셜오일을 비롯 첨가물 넣기
+8. 블랜더하고 스푼으로 마무리</t>
+        </is>
+      </c>
       <c r="I245" s="7" t="n"/>
       <c r="J245" s="6" t="inlineStr">
         <is>

--- a/허브누리_레시피_목록_상세_p4of6_썸네일.xlsx
+++ b/허브누리_레시피_목록_상세_p4of6_썸네일.xlsx
@@ -6164,7 +6164,7 @@
       <row>132</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="241" name="Image 241" descr="Picture"/>
@@ -8214,7 +8214,7 @@
       <row>217</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="323" name="Image 323" descr="Picture"/>
@@ -8514,7 +8514,7 @@
       <row>232</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="904875"/>
+    <ext cx="1047750" cy="895350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="335" name="Image 335" descr="Picture"/>
@@ -8689,7 +8689,7 @@
       <row>242</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="847725"/>
+    <ext cx="1047750" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="342" name="Image 342" descr="Picture"/>
@@ -8739,7 +8739,7 @@
       <row>244</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="904875"/>
+    <ext cx="1047750" cy="895350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="344" name="Image 344" descr="Picture"/>
@@ -8789,7 +8789,7 @@
       <row>244</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="323850"/>
+    <ext cx="1047750" cy="333375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="346" name="Image 346" descr="Picture"/>
@@ -12864,7 +12864,7 @@
       <row>398</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="509" name="Image 509" descr="Picture"/>
@@ -16339,7 +16339,7 @@
       <row>515</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="648" name="Image 648" descr="Picture"/>
@@ -16489,7 +16489,7 @@
       <row>519</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="654" name="Image 654" descr="Picture"/>
@@ -16639,7 +16639,7 @@
       <row>524</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="660" name="Image 660" descr="Picture"/>
